--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK118"/>
+  <dimension ref="A1:AK132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45947.29513888889</v>
+        <v>45947.29166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45947.3125</v>
+        <v>45947.29513888889</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45947.35416666666</v>
+        <v>45947.3125</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45947.35763888889</v>
+        <v>45947.35416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45947.375</v>
+        <v>45947.35763888889</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45947.41666666666</v>
+        <v>45947.375</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45947.42013888889</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45947.42013888889</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45947.42708333334</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45947.43055555555</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45947.4375</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.42013888889</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.42013888889</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.42708333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.43055555555</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.4375</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="34">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.50347222222</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.50694444445</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45947.50694444445</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="51">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,55 +7506,55 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N55" t="n">
+        <v>14</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
         <v>2.3</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="58">
@@ -7852,27 +7852,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="60">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9400,27 +9400,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="82">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,27 +12367,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,10 +12828,10 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="99">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,10 +13989,10 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="107">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="108">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45947.66666666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="113">
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45947.67708333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="114">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45947.79166666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45947.83333333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="117">
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45947.95833333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="118">
@@ -15592,126 +15592,1932 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK118" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Belgium Pro League</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Standard Liège</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Royal Antwerp FC</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N119" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK119" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK120" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Longford Town</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
+        <v>45947.66666666666</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK124" s="3" t="n">
+        <v>45947.66666666666</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Spain Primera Division RFEF Group 2</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>FC Cartagena</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Algeciras CF</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
+        <v>45947.67708333334</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="3" t="n">
+        <v>45947.75</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Santiago Morning</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" s="3" t="n">
+        <v>45947.75</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" s="3" t="n">
+        <v>45947.79166666666</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" s="3" t="n">
+        <v>45947.83333333334</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>3</v>
+      </c>
+      <c r="M130" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK130" s="3" t="n">
+        <v>45947.85416666666</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK131" s="3" t="n">
+        <v>45947.95833333334</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="inlineStr">
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" s="3" t="n">
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="3" t="n">
         <v>45947.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N50" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,10 +13602,10 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,10 +13989,10 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK132"/>
+  <dimension ref="A1:AK148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45947.41666666666</v>
+        <v>45947.375</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45947.42013888889</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45947.42013888889</v>
+        <v>45947.41666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45947.42708333334</v>
+        <v>45947.42013888889</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45947.43055555555</v>
+        <v>45947.42013888889</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45947.4375</v>
+        <v>45947.42708333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.43055555555</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.4375</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.4375</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45947.50347222222</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45947.50694444445</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.46875</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.50347222222</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.50694444445</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="56">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="M65" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>4.91</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10119,10 +10119,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,27 +10561,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="80">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="81">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="83">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="85">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11667,10 +11667,10 @@
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="95">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="100">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="102">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="M102" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N102" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="113">
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N116" t="n">
         <v>3.05</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15537,10 +15537,10 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="120">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,27 +15979,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45947.66666666666</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45947.66666666666</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,27 +16495,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45947.67708333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="126">
@@ -16624,27 +16624,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,16 +16704,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="127">
@@ -16753,27 +16753,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="128">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45947.79166666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45947.83333333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45947.85416666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="131">
@@ -17269,27 +17269,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45947.95833333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="132">
@@ -17398,126 +17398,2190 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Drogheda United</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Republic of Ireland First Division</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Wexford</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Galway United</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Portadown</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Linfield</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
+        <v>45947.65625</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>RCD Espanyol</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" s="3" t="n">
+        <v>45947.66666666666</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" s="3" t="n">
+        <v>45947.66666666666</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Spain Primera Division RFEF Group 2</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>FC Cartagena</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Algeciras CF</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="3" t="n">
+        <v>45947.67708333334</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Santiago Morning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK142" s="3" t="n">
+        <v>45947.75</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK143" s="3" t="n">
+        <v>45947.75</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" s="3" t="n">
+        <v>45947.79166666666</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK145" s="3" t="n">
+        <v>45947.83333333334</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK146" s="3" t="n">
+        <v>45947.85416666666</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" s="3" t="n">
+        <v>45947.95833333334</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="inlineStr">
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" s="3" t="n">
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK148" s="3" t="n">
         <v>45947.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK148"/>
+  <dimension ref="A1:AK144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.46875</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45947.46875</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.50347222222</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.50694444445</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45947.50347222222</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45947.50694444445</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="56">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="70">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9529,27 +9529,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,16 +9609,16 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,27 +9658,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.97</v>
+        <v>5.3</v>
       </c>
       <c r="M75" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10119,16 +10119,16 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="M77" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="N77" t="n">
-        <v>1.58</v>
+        <v>3.65</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10377,16 +10377,16 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="N78" t="n">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10561,27 +10561,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="80">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="81">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="83">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M83" t="n">
         <v>2.95</v>
       </c>
       <c r="N83" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11243,17 +11243,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M85" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="M86" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N86" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M87" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="N87" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11667,16 +11667,16 @@
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N89" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.65</v>
+        <v>2.69</v>
       </c>
       <c r="M93" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N93" t="n">
-        <v>4.9</v>
+        <v>2.71</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="95">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N108" t="n">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="M109" t="n">
         <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Z109" t="n">
         <v>1.88</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="M110" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N110" t="n">
-        <v>3.44</v>
+        <v>2.52</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="M112" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="N112" t="n">
-        <v>5.35</v>
+        <v>4.3</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N113" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="115">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M117" t="n">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="N117" t="n">
-        <v>3.55</v>
+        <v>3.73</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15537,16 +15537,16 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="M119" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N119" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15795,16 +15795,16 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15979,27 +15979,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z121" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="122">
@@ -16108,27 +16108,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,16 +16317,16 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="124">
@@ -16366,27 +16366,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N124" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="125">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.28</v>
+        <v>2.65</v>
       </c>
       <c r="M126" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>9.5</v>
+        <v>2.45</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,16 +16704,16 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="M127" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N127" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="M131" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N131" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17785,27 +17785,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="AK135" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.66666666666</v>
       </c>
     </row>
     <row r="136">
@@ -17914,27 +17914,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.66666666666</v>
       </c>
     </row>
     <row r="137">
@@ -18043,27 +18043,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="AK137" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.67708333334</v>
       </c>
     </row>
     <row r="138">
@@ -18172,27 +18172,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18292,7 +18292,7 @@
         <v>0</v>
       </c>
       <c r="AK138" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.75</v>
       </c>
     </row>
     <row r="139">
@@ -18301,27 +18301,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18421,7 +18421,7 @@
         <v>0</v>
       </c>
       <c r="AK139" s="3" t="n">
-        <v>45947.66666666666</v>
+        <v>45947.75</v>
       </c>
     </row>
     <row r="140">
@@ -18430,27 +18430,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M140" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N140" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18550,7 +18550,7 @@
         <v>0</v>
       </c>
       <c r="AK140" s="3" t="n">
-        <v>45947.66666666666</v>
+        <v>45947.79166666666</v>
       </c>
     </row>
     <row r="141">
@@ -18559,27 +18559,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18679,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="AK141" s="3" t="n">
-        <v>45947.67708333334</v>
+        <v>45947.83333333334</v>
       </c>
     </row>
     <row r="142">
@@ -18688,12 +18688,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18808,7 +18808,7 @@
         <v>0</v>
       </c>
       <c r="AK142" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.85416666666</v>
       </c>
     </row>
     <row r="143">
@@ -18817,12 +18817,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Z143" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18937,7 +18937,7 @@
         <v>0</v>
       </c>
       <c r="AK143" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.95833333334</v>
       </c>
     </row>
     <row r="144">
@@ -18946,12 +18946,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19066,522 +19066,6 @@
         <v>0</v>
       </c>
       <c r="AK144" s="3" t="n">
-        <v>45947.79166666666</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK145" s="3" t="n">
-        <v>45947.83333333334</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L146" t="n">
-        <v>3</v>
-      </c>
-      <c r="M146" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N146" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK146" s="3" t="n">
-        <v>45947.85416666666</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK147" s="3" t="n">
-        <v>45947.95833333334</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK148" s="3" t="n">
         <v>45947.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK144"/>
+  <dimension ref="A1:AK132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45947.41666666666</v>
+        <v>45947.42013888889</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45947.42013888889</v>
+        <v>45947.42708333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45947.42708333334</v>
+        <v>45947.43055555555</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45947.43055555555</v>
+        <v>45947.4375</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45947.4375</v>
+        <v>45947.45833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.46875</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.47916666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45947.45833333334</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45947.46875</v>
+        <v>45947.5</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.50347222222</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45947.47916666666</v>
+        <v>45947.50694444445</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45947.5</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45947.50347222222</v>
+        <v>45947.52083333334</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45947.50694444445</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.53125</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45947.52083333334</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.35</v>
+        <v>2.17</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="N52" t="n">
-        <v>1.98</v>
+        <v>2.76</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.3</v>
+        <v>1.83</v>
       </c>
       <c r="M56" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N56" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>5.7</v>
+        <v>3.69</v>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>3.59</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.17</v>
+        <v>4.8</v>
       </c>
       <c r="M61" t="n">
-        <v>3.37</v>
+        <v>3.97</v>
       </c>
       <c r="N61" t="n">
-        <v>2.76</v>
+        <v>1.51</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>1.65</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="M66" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N66" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8958,16 +8958,16 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,27 +9529,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="M71" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N71" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,10 +9603,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="72">
@@ -9658,27 +9658,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N72" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M74" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>4.91</v>
+        <v>4.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.3</v>
+        <v>1.65</v>
       </c>
       <c r="M75" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
         <v>2.95</v>
       </c>
       <c r="N77" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10377,16 +10377,16 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="M78" t="n">
         <v>2.95</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45947.58333333334</v>
+        <v>45947.60416666666</v>
       </c>
     </row>
     <row r="79">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N80" t="n">
-        <v>4.15</v>
+        <v>3.12</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="82">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="83">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="85">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="N85" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M86" t="n">
-        <v>3.7</v>
+        <v>2.97</v>
       </c>
       <c r="N86" t="n">
-        <v>5.4</v>
+        <v>2.61</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="M88" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="M89" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.75</v>
+        <v>4.3</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N90" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45947.60416666666</v>
+        <v>45947.625</v>
       </c>
     </row>
     <row r="91">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="M93" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="N93" t="n">
-        <v>2.71</v>
+        <v>2.24</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N97" t="n">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.63541666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>2.45</v>
+        <v>3.52</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="N103" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="N104" t="n">
-        <v>5.35</v>
+        <v>3.73</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,10 +14118,10 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="M107" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>2.1</v>
+        <v>3.09</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="M108" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45947.625</v>
+        <v>45947.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.94</v>
+        <v>1.45</v>
       </c>
       <c r="M109" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N109" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M110" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N110" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45947.63541666666</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="111">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>4.3</v>
+        <v>2.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M113" t="n">
-        <v>3.65</v>
+        <v>3.09</v>
       </c>
       <c r="N113" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="115">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M118" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="N118" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="119">
@@ -15721,27 +15721,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,14 +15762,14 @@
         </is>
       </c>
       <c r="L119" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N119" t="n">
         <v>2.25</v>
       </c>
-      <c r="M119" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N119" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O119" t="n">
         <v>0</v>
       </c>
@@ -15795,16 +15795,16 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="120">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="M120" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N120" t="n">
-        <v>3.52</v>
+        <v>2.45</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45947.64583333334</v>
+        <v>45947.65625</v>
       </c>
     </row>
     <row r="121">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.28</v>
+        <v>2.79</v>
       </c>
       <c r="M123" t="n">
-        <v>6</v>
+        <v>3.23</v>
       </c>
       <c r="N123" t="n">
-        <v>9.5</v>
+        <v>2.49</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,16 +16317,16 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.66666666666</v>
       </c>
     </row>
     <row r="124">
@@ -16366,27 +16366,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.66666666666</v>
       </c>
     </row>
     <row r="125">
@@ -16495,27 +16495,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.67708333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.75</v>
       </c>
     </row>
     <row r="127">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.75</v>
       </c>
     </row>
     <row r="128">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="M128" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N128" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.79166666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.83333333334</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="M130" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="N130" t="n">
-        <v>4.6</v>
+        <v>2.37</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.85416666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,27 +17269,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="M131" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N131" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45947.65625</v>
+        <v>45947.95833333334</v>
       </c>
     </row>
     <row r="132">
@@ -17398,27 +17398,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17442,10 +17442,10 @@
         <v>2.4</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17518,1554 +17518,6 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45947.65625</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Northern Ireland NIFL Premiership</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Portadown</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Linfield</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3" t="n">
-        <v>45947.65625</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Republic of Ireland First Division</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Finn Harps</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>UCD</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK134" s="3" t="n">
-        <v>45947.65625</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Ipswich Town</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" s="3" t="n">
-        <v>45947.66666666666</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>RCD Espanyol</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK136" s="3" t="n">
-        <v>45947.66666666666</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Spain Primera Division RFEF Group 2</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>FC Cartagena</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Algeciras CF</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK137" s="3" t="n">
-        <v>45947.67708333334</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Santiago Morning</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Cobreloa</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3" t="n">
-        <v>45947.75</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK139" s="3" t="n">
-        <v>45947.75</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M140" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N140" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK140" s="3" t="n">
-        <v>45947.79166666666</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK141" s="3" t="n">
-        <v>45947.83333333334</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>3</v>
-      </c>
-      <c r="M142" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N142" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK142" s="3" t="n">
-        <v>45947.85416666666</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M143" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N143" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK143" s="3" t="n">
-        <v>45947.95833333334</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M144" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N144" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK144" s="3" t="n">
         <v>45947.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.32</v>
+        <v>5.7</v>
       </c>
       <c r="N47" t="n">
-        <v>2.69</v>
+        <v>14</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="M52" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="N52" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.25</v>
+        <v>2.57</v>
       </c>
       <c r="M54" t="n">
-        <v>5.7</v>
+        <v>3.26</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>2.36</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M60" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="N60" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.8</v>
+        <v>1.97</v>
       </c>
       <c r="M61" t="n">
-        <v>3.97</v>
+        <v>2.95</v>
       </c>
       <c r="N61" t="n">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="M62" t="n">
-        <v>4.4</v>
+        <v>3.97</v>
       </c>
       <c r="N62" t="n">
-        <v>7.4</v>
+        <v>1.51</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,16 +8448,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,17 +9308,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,10 +9345,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M71" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N71" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9702,10 +9702,10 @@
         <v>1.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="N74" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="N75" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="M76" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M77" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="N77" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10386,7 +10386,7 @@
         <v>2.35</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10469,17 +10469,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N79" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="N80" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10773,7 +10773,7 @@
         <v>2.35</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="M85" t="n">
-        <v>3.31</v>
+        <v>2.97</v>
       </c>
       <c r="N85" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4.3</v>
+        <v>2.41</v>
       </c>
       <c r="M90" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N90" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="O90" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="Z90" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,10 +14118,10 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="N107" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="M109" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="N109" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14514,7 +14514,7 @@
         <v>1.72</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.45</v>
+        <v>3.09</v>
       </c>
       <c r="N110" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="M111" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="N111" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,16 +14769,16 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N112" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>5.9</v>
+        <v>2.85</v>
       </c>
       <c r="N114" t="n">
-        <v>8.9</v>
+        <v>3</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N115" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="M116" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N116" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="M118" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M119" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N119" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="Z119" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M128" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N128" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M131" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N131" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N132" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.02</v>
+        <v>1.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N51" t="n">
-        <v>2.02</v>
+        <v>14</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.57</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="N54" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M58" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="N58" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
         <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9216,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M69" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N70" t="n">
-        <v>4.15</v>
+        <v>3.12</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="M71" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="N72" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M74" t="n">
-        <v>3.76</v>
+        <v>2.9</v>
       </c>
       <c r="N74" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10082,17 +10082,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="M77" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>3.12</v>
+        <v>5.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10469,17 +10469,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>5.4</v>
+        <v>4.15</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M80" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N80" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M94" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="N94" t="n">
-        <v>3.57</v>
+        <v>2.61</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
         <v>1.68</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="M95" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="M97" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N98" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>3.09</v>
+        <v>3.52</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="N101" t="n">
-        <v>3.52</v>
+        <v>3.73</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="M103" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="N105" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M109" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="M110" t="n">
-        <v>3.09</v>
+        <v>5.9</v>
       </c>
       <c r="N110" t="n">
-        <v>3.03</v>
+        <v>8.9</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="M111" t="n">
-        <v>5.9</v>
+        <v>3.09</v>
       </c>
       <c r="N111" t="n">
-        <v>8.9</v>
+        <v>3.03</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,16 +14769,16 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,49 +14859,49 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N112" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
         <v>1.72</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N112" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z112" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="M116" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N116" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="M31" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="M48" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.69</v>
+        <v>2.02</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6645,7 +6645,7 @@
         <v>1.67</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="M53" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N53" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="M62" t="n">
-        <v>3.97</v>
+        <v>2.59</v>
       </c>
       <c r="N62" t="n">
-        <v>1.51</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8442,16 +8442,16 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="M63" t="n">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="N64" t="n">
-        <v>7.4</v>
+        <v>3.89</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,10 +8700,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8958,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9216,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="M70" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="N70" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>4.9</v>
+        <v>4.15</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M74" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N74" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10082,17 +10082,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M76" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N76" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10248,16 +10248,16 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N77" t="n">
-        <v>5.4</v>
+        <v>2.95</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="N78" t="n">
-        <v>5.1</v>
+        <v>3.12</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N79" t="n">
-        <v>4.15</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.92</v>
+        <v>3.02</v>
       </c>
       <c r="M88" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="N88" t="n">
-        <v>3.57</v>
+        <v>2.24</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="M94" t="n">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="N94" t="n">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>3.52</v>
+        <v>3.09</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.62</v>
+        <v>2.46</v>
       </c>
       <c r="M105" t="n">
-        <v>3.74</v>
+        <v>2.93</v>
       </c>
       <c r="N105" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.46</v>
+        <v>2.11</v>
       </c>
       <c r="M107" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="N107" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="N108" t="n">
-        <v>3.09</v>
+        <v>4.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,55 +14472,55 @@
         </is>
       </c>
       <c r="L109" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M109" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N109" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z109" t="n">
         <v>2.75</v>
       </c>
-      <c r="M109" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N109" t="n">
-        <v>3</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="M110" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>8.9</v>
+        <v>2.35</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="N112" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         <v>1.72</v>
       </c>
       <c r="Z112" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.72</v>
+        <v>2.75</v>
       </c>
       <c r="M116" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="N116" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.45</v>
+        <v>4.3</v>
       </c>
       <c r="M117" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="N117" t="n">
-        <v>7</v>
+        <v>1.82</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="M119" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N119" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="M122" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N122" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="M131" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N131" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M132" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.25</v>
+        <v>3.02</v>
       </c>
       <c r="M47" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>14</v>
+        <v>2.02</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.02</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N48" t="n">
-        <v>2.02</v>
+        <v>2.76</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>3.37</v>
+        <v>5.7</v>
       </c>
       <c r="N54" t="n">
-        <v>2.76</v>
+        <v>14</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="N60" t="n">
-        <v>3.9</v>
+        <v>3.59</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="M61" t="n">
-        <v>3.97</v>
+        <v>2.87</v>
       </c>
       <c r="N61" t="n">
-        <v>1.51</v>
+        <v>3.89</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,16 +8313,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
-        <v>3.21</v>
+        <v>2.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8442,10 +8442,10 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="M63" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="N63" t="n">
-        <v>7.4</v>
+        <v>3.21</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8571,10 +8571,10 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -8583,10 +8583,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,10 +8700,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="N65" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,16 +8835,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>3.97</v>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M69" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="M70" t="n">
-        <v>3.76</v>
+        <v>2.9</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="N72" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="M74" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M76" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N76" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10248,16 +10248,16 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M77" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>2.95</v>
+        <v>5.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="M78" t="n">
-        <v>3.04</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>3.12</v>
+        <v>4.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,49 +10602,49 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z79" t="n">
         <v>1.6</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N79" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.72</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.3</v>
+        <v>2.41</v>
       </c>
       <c r="M84" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N84" t="n">
-        <v>1.72</v>
+        <v>2.48</v>
       </c>
       <c r="O84" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="M91" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="N91" t="n">
-        <v>3.57</v>
+        <v>1.72</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="M97" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N97" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="M98" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M99" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>3.73</v>
+        <v>2.75</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>3.09</v>
+        <v>3.52</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>3.52</v>
+        <v>3.09</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="M105" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N105" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>2.46</v>
       </c>
       <c r="M108" t="n">
-        <v>3.74</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="M109" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>8.9</v>
+        <v>1.76</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,16 +14511,16 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N110" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="M111" t="n">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="N111" t="n">
-        <v>3.03</v>
+        <v>2.26</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="M112" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>2.24</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="M113" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="N113" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="Z113" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>1.59</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>3.67</v>
       </c>
       <c r="N115" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.75</v>
+        <v>6.3</v>
       </c>
       <c r="M116" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.3</v>
+        <v>2.34</v>
       </c>
       <c r="M117" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N117" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="M119" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N119" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="M120" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="N120" t="n">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="M122" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="N122" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17085,10 +17085,10 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X129" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,10 +17310,10 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M131" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N131" t="n">
         <v>2.55</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N132" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -714,10 +714,10 @@
         <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.02</v>
+        <v>1.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N47" t="n">
-        <v>2.02</v>
+        <v>14</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.25</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
-        <v>5.7</v>
+        <v>3.37</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>2.76</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="M62" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.37</v>
+        <v>1.4</v>
       </c>
       <c r="M63" t="n">
-        <v>2.59</v>
+        <v>4.4</v>
       </c>
       <c r="N63" t="n">
-        <v>3.21</v>
+        <v>7.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8571,10 +8571,10 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -8583,10 +8583,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8841,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="M66" t="n">
-        <v>3.97</v>
+        <v>2.87</v>
       </c>
       <c r="N66" t="n">
-        <v>1.51</v>
+        <v>3.89</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8958,16 +8958,16 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.01</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="M70" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N70" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="N72" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N74" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N75" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>5.1</v>
+        <v>4.15</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10340,17 +10340,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N78" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M80" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N80" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.41</v>
+        <v>3.11</v>
       </c>
       <c r="M84" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N84" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="M91" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="N91" t="n">
-        <v>1.72</v>
+        <v>2.61</v>
       </c>
       <c r="O91" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="M97" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N98" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="N99" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="M101" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="M103" t="n">
         <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>3.45</v>
+        <v>3.09</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M105" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="N105" t="n">
-        <v>2.95</v>
+        <v>3.73</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="M106" t="n">
-        <v>3.56</v>
+        <v>2.93</v>
       </c>
       <c r="N106" t="n">
-        <v>3.73</v>
+        <v>3.1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="M107" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N107" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.87</v>
+        <v>1.41</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N109" t="n">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="M111" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="N111" t="n">
-        <v>2.26</v>
+        <v>2.87</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.81</v>
+        <v>3.87</v>
       </c>
       <c r="M112" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="M113" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="N113" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="M114" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="N114" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.59</v>
+        <v>6.3</v>
       </c>
       <c r="M115" t="n">
-        <v>3.67</v>
+        <v>4.3</v>
       </c>
       <c r="N115" t="n">
-        <v>4.6</v>
+        <v>1.45</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>6.3</v>
+        <v>2.65</v>
       </c>
       <c r="M116" t="n">
-        <v>4.3</v>
+        <v>3.39</v>
       </c>
       <c r="N116" t="n">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.34</v>
+        <v>1.27</v>
       </c>
       <c r="M117" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="N117" t="n">
-        <v>2.49</v>
+        <v>8.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.95</v>
+        <v>1.85</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N118" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="M119" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N119" t="n">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="M120" t="n">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="N120" t="n">
-        <v>3.03</v>
+        <v>2.26</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="M121" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N121" t="n">
-        <v>5.7</v>
+        <v>2.49</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="M122" t="n">
-        <v>5.9</v>
+        <v>3.67</v>
       </c>
       <c r="N122" t="n">
-        <v>8.9</v>
+        <v>4.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>2.4</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.25</v>
+        <v>2.57</v>
       </c>
       <c r="M47" t="n">
-        <v>5.7</v>
+        <v>3.26</v>
       </c>
       <c r="N47" t="n">
-        <v>14</v>
+        <v>2.36</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="N49" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N50" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.02</v>
+        <v>1.36</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="M62" t="n">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,16 +8448,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8583,10 +8583,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>3.89</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8958,16 +8958,16 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="N68" t="n">
-        <v>2.3</v>
+        <v>3.89</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9216,16 +9216,16 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N69" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N70" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="M72" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="N72" t="n">
-        <v>5.1</v>
+        <v>3.12</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>2.95</v>
       </c>
       <c r="N73" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,17 +9953,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="M75" t="n">
-        <v>2.95</v>
+        <v>3.76</v>
       </c>
       <c r="N75" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N76" t="n">
-        <v>4.15</v>
+        <v>5.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10340,17 +10340,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="M78" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N82" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.02</v>
+        <v>4.3</v>
       </c>
       <c r="M92" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="N92" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P92" t="n">
         <v>2.24</v>
       </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="M93" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>3.57</v>
+        <v>2.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="M97" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N97" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="M98" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M101" t="n">
         <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="M102" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N103" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="M106" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="N106" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="M107" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="M108" t="n">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="N108" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="M109" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="N109" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="M110" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N110" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z110" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1.6</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.41</v>
+        <v>6.3</v>
       </c>
       <c r="M111" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="N111" t="n">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="N112" t="n">
-        <v>1.76</v>
+        <v>3.03</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="M113" t="n">
         <v>3.15</v>
       </c>
       <c r="N113" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="M114" t="n">
-        <v>3.09</v>
+        <v>3.45</v>
       </c>
       <c r="N114" t="n">
-        <v>3.03</v>
+        <v>2.49</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>6.3</v>
+        <v>1.27</v>
       </c>
       <c r="M115" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="N115" t="n">
-        <v>1.45</v>
+        <v>8.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="M116" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="N116" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="M117" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>8.9</v>
+        <v>3.55</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="M118" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N118" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="M119" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N119" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.66</v>
+        <v>3.87</v>
       </c>
       <c r="M120" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N120" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="M121" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N121" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="M122" t="n">
-        <v>3.67</v>
+        <v>2.8</v>
       </c>
       <c r="N122" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M131" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N131" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M132" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N132" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK132"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4419,52 +4419,52 @@
         <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X31" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5322,34 +5322,34 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y38" t="n">
         <v>1.7</v>
@@ -5358,16 +5358,16 @@
         <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,52 +5451,52 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45947.53125</v>
+        <v>45947.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.25</v>
+        <v>3.02</v>
       </c>
       <c r="M48" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>14</v>
+        <v>2.02</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="M49" t="n">
-        <v>3.37</v>
+        <v>5.7</v>
       </c>
       <c r="N49" t="n">
-        <v>2.76</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.24</v>
+        <v>2.57</v>
       </c>
       <c r="M50" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.02</v>
+        <v>2.17</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N53" t="n">
-        <v>2.02</v>
+        <v>2.76</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45947.54166666666</v>
+        <v>45947.5625</v>
       </c>
     </row>
     <row r="56">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="M60" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>3.59</v>
+        <v>2.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45947.5625</v>
+        <v>45947.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="M61" t="n">
-        <v>3.01</v>
+        <v>3.97</v>
       </c>
       <c r="N61" t="n">
-        <v>4.7</v>
+        <v>1.51</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="M69" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M70" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="N71" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="M72" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N72" t="n">
-        <v>3.12</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9732,16 +9732,16 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,17 +9953,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M75" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>5.4</v>
+        <v>4.15</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N77" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10469,17 +10469,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N79" t="n">
-        <v>4.15</v>
+        <v>3.12</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M80" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N80" t="n">
-        <v>2.95</v>
+        <v>5.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="M82" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="N82" t="n">
-        <v>2.61</v>
+        <v>2.24</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,61 +12795,61 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.41</v>
+        <v>4.3</v>
       </c>
       <c r="M96" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="M97" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N98" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="M99" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>4.3</v>
+        <v>3.09</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N101" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="M103" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="M104" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="M105" t="n">
-        <v>3.56</v>
+        <v>2.93</v>
       </c>
       <c r="N105" t="n">
-        <v>3.73</v>
+        <v>3.1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M106" t="n">
         <v>3.25</v>
       </c>
       <c r="N106" t="n">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="N107" t="n">
-        <v>3.09</v>
+        <v>3.73</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.46</v>
+        <v>1.62</v>
       </c>
       <c r="M108" t="n">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="N108" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.45</v>
+        <v>2.02</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.59</v>
+        <v>2.66</v>
       </c>
       <c r="M109" t="n">
-        <v>3.67</v>
+        <v>3.32</v>
       </c>
       <c r="N109" t="n">
-        <v>4.6</v>
+        <v>2.26</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.65</v>
+        <v>6.3</v>
       </c>
       <c r="M110" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N110" t="n">
-        <v>2.23</v>
+        <v>1.45</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>6.3</v>
+        <v>2.75</v>
       </c>
       <c r="M111" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N111" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="M112" t="n">
-        <v>3.09</v>
+        <v>3.67</v>
       </c>
       <c r="N112" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="M113" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="M114" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>2.49</v>
+        <v>3.69</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.27</v>
+        <v>2.34</v>
       </c>
       <c r="M115" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="N115" t="n">
-        <v>8.9</v>
+        <v>2.49</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="M116" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="M117" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N117" t="n">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.81</v>
+        <v>3.87</v>
       </c>
       <c r="M119" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N119" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="M120" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="N120" t="n">
-        <v>1.76</v>
+        <v>3.03</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.95</v>
+        <v>1.27</v>
       </c>
       <c r="M121" t="n">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="N121" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,16 +16059,16 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="M122" t="n">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="N122" t="n">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16624,27 +16624,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45947.75</v>
+        <v>45947.67708333334</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="M128" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45947.79166666666</v>
+        <v>45947.75</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M129" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N129" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17085,16 +17085,16 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45947.83333333334</v>
+        <v>45947.79166666666</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="M130" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="N130" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17214,16 +17214,16 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45947.85416666666</v>
+        <v>45947.83333333334</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M131" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N131" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45947.95833333334</v>
+        <v>45947.85416666666</v>
       </c>
     </row>
     <row r="132">
@@ -17518,6 +17518,135 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
+        <v>45947.95833333334</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M133" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
         <v>45947.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-10-17.xlsx
+++ b/jogos_2025-10-17.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N2" t="n">
         <v>2.45</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>2.85</v>
@@ -708,16 +708,16 @@
         <v>4.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
         <v>1.46</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>7.75</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>2.83</v>
@@ -1224,16 +1224,16 @@
         <v>5</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.59</v>
       </c>
       <c r="AC6" t="n">
         <v>1.43</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="M9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.53</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>4.83</v>
+        <v>1.73</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>7.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="T25" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.15</v>
+        <v>3.15</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,62 +3765,62 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9</v>
+        <v>4.15</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
-        <v>1.73</v>
+        <v>4.83</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.01</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="T26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2.19</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.15</v>
+        <v>1.15</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>1.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X31" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y31" t="n">
         <v>3.1</v>
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.5</v>
+        <v>5.47</v>
       </c>
       <c r="M33" t="n">
-        <v>5.2</v>
+        <v>5.54</v>
       </c>
       <c r="N33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5838,34 +5838,34 @@
         <v>2.7</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y42" t="n">
         <v>1.8</v>
@@ -5874,16 +5874,16 @@
         <v>2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N48" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,62 +6732,62 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.25</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>5.7</v>
+        <v>3.37</v>
       </c>
       <c r="N49" t="n">
-        <v>14</v>
+        <v>2.76</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD49" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.57</v>
+        <v>2.24</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N50" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="M53" t="n">
-        <v>3.37</v>
+        <v>4.4</v>
       </c>
       <c r="N53" t="n">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,28 +7281,28 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="M56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q56" t="n">
         <v>3.69</v>
       </c>
-      <c r="N56" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="M61" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8442,16 +8442,16 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8571,16 +8571,16 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="M66" t="n">
-        <v>3.01</v>
+        <v>3.97</v>
       </c>
       <c r="N66" t="n">
-        <v>4.7</v>
+        <v>1.51</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC66" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="M67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA67" t="n">
         <v>2.59</v>
       </c>
-      <c r="N67" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="M68" t="n">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="N68" t="n">
-        <v>3.89</v>
+        <v>7.4</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W68" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="X68" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>3.76</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,62 +9699,62 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD72" t="n">
         <v>1.9</v>
       </c>
-      <c r="M72" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N72" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X72" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
       <c r="AE72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="N73" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="N74" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,61 +10086,61 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N75" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N76" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M77" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N77" t="n">
-        <v>2.95</v>
+        <v>4.9</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10469,65 +10469,65 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10611,34 +10611,34 @@
         <v>3.12</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y79" t="n">
         <v>2.35</v>
@@ -10647,16 +10647,16 @@
         <v>1.6</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M80" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N80" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10764,16 +10764,16 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.41</v>
+        <v>3.11</v>
       </c>
       <c r="M86" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,61 +11634,61 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.92</v>
+        <v>3.02</v>
       </c>
       <c r="M87" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="N87" t="n">
-        <v>3.57</v>
+        <v>2.24</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,61 +12537,61 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,61 +12666,61 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,61 +12795,61 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N99" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N100" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="M101" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="M105" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M106" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="N106" t="n">
-        <v>2.75</v>
+        <v>3.73</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="M107" t="n">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="N107" t="n">
-        <v>3.73</v>
+        <v>4.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="M108" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N108" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,61 +14472,61 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="M109" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="N109" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
@@ -14539,10 +14539,10 @@
         </is>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,61 +14601,61 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>6.3</v>
+        <v>2.81</v>
       </c>
       <c r="M110" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N110" t="n">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
@@ -14668,10 +14668,10 @@
         </is>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH110" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,61 +14730,61 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="M111" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,61 +14859,61 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.59</v>
+        <v>2.34</v>
       </c>
       <c r="M112" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>4.6</v>
+        <v>2.49</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="M113" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N113" t="n">
-        <v>2.22</v>
+        <v>5.7</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Z113" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>3.69</v>
+        <v>2.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,61 +15246,61 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="M115" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="N115" t="n">
-        <v>2.49</v>
+        <v>4.6</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.81</v>
+        <v>6.3</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N116" t="n">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,61 +15504,61 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.41</v>
+        <v>3.87</v>
       </c>
       <c r="M117" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N117" t="n">
-        <v>2.87</v>
+        <v>1.76</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y117" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
@@ -15571,10 +15571,10 @@
         </is>
       </c>
       <c r="AG117" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH117" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,61 +15633,61 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.41</v>
+        <v>2.41</v>
       </c>
       <c r="M118" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="N118" t="n">
-        <v>5.7</v>
+        <v>2.87</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
@@ -15700,10 +15700,10 @@
         </is>
       </c>
       <c r="AG118" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH118" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,77 +15762,77 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.87</v>
+        <v>1.8</v>
       </c>
       <c r="M119" t="n">
         <v>3.4</v>
       </c>
       <c r="N119" t="n">
-        <v>1.76</v>
+        <v>3.69</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Z119" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH119" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>0</v>
       </c>
       <c r="AI119" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,61 +16149,61 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="M122" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="N122" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,61 +16794,61 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
@@ -16861,10 +16861,10 @@
         </is>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH127" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M132" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N132" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M133" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
